--- a/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0003T0006Z000C1N6_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0003T0006Z000C1N6_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>70.48696898982274</v>
+        <v>11.4541324608462</v>
       </c>
       <c r="D2" t="n">
-        <v>64.36887864295318</v>
+        <v>10.45994277947989</v>
       </c>
       <c r="E2" t="n">
-        <v>19.06362136088575</v>
+        <v>3.097838471143935</v>
       </c>
       <c r="F2" t="n">
-        <v>19.07075957399037</v>
+        <v>3.098998430773434</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>74.71366889329168</v>
+        <v>12.1409711951599</v>
       </c>
       <c r="D3" t="n">
-        <v>68.14342769197533</v>
+        <v>11.07330699994599</v>
       </c>
       <c r="E3" t="n">
-        <v>19.06362136088575</v>
+        <v>3.097838471143935</v>
       </c>
       <c r="F3" t="n">
-        <v>19.07075957399037</v>
+        <v>3.098998430773434</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>66.96384691235865</v>
+        <v>10.88162512325828</v>
       </c>
       <c r="D4" t="n">
-        <v>61.28580073651825</v>
+        <v>9.958942619684215</v>
       </c>
       <c r="E4" t="n">
-        <v>19.06362136088575</v>
+        <v>3.097838471143935</v>
       </c>
       <c r="F4" t="n">
-        <v>19.07075957399037</v>
+        <v>3.098998430773434</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>62.12093575319953</v>
+        <v>10.09465205989492</v>
       </c>
       <c r="D5" t="n">
-        <v>58.8327863886722</v>
+        <v>9.560327788159233</v>
       </c>
       <c r="E5" t="n">
-        <v>19.06362136088575</v>
+        <v>3.097838471143935</v>
       </c>
       <c r="F5" t="n">
-        <v>19.07075957399037</v>
+        <v>3.098998430773434</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>25.82116857400744</v>
+        <v>4.195939893276209</v>
       </c>
       <c r="D6" t="n">
-        <v>19.25529470637153</v>
+        <v>3.128985389785374</v>
       </c>
       <c r="E6" t="n">
-        <v>19.06362136088575</v>
+        <v>3.097838471143935</v>
       </c>
       <c r="F6" t="n">
-        <v>19.07075957399037</v>
+        <v>3.098998430773434</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>26.24787194270385</v>
+        <v>4.265279190689376</v>
       </c>
       <c r="D7" t="n">
-        <v>21.11784249169059</v>
+        <v>3.431649404899721</v>
       </c>
       <c r="E7" t="n">
-        <v>19.06362136088575</v>
+        <v>3.097838471143935</v>
       </c>
       <c r="F7" t="n">
-        <v>19.07075957399037</v>
+        <v>3.098998430773434</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>19.16577029874272</v>
+        <v>3.114437673545692</v>
       </c>
       <c r="D8" t="n">
-        <v>19.71785215844517</v>
+        <v>3.204150975747341</v>
       </c>
       <c r="E8" t="n">
-        <v>19.06362136088575</v>
+        <v>3.097838471143935</v>
       </c>
       <c r="F8" t="n">
-        <v>19.07075957399037</v>
+        <v>3.098998430773434</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>25.02685112453442</v>
+        <v>4.066863307736844</v>
       </c>
       <c r="D9" t="n">
-        <v>27.95770766898928</v>
+        <v>4.543127496210759</v>
       </c>
       <c r="E9" t="n">
-        <v>19.06362136088575</v>
+        <v>3.097838471143935</v>
       </c>
       <c r="F9" t="n">
-        <v>19.07075957399037</v>
+        <v>3.098998430773434</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>18.70113559021238</v>
+        <v>3.038934533409513</v>
       </c>
       <c r="D10" t="n">
-        <v>17.4351781700421</v>
+        <v>2.833216452631842</v>
       </c>
       <c r="E10" t="n">
-        <v>19.06362136088575</v>
+        <v>3.097838471143935</v>
       </c>
       <c r="F10" t="n">
-        <v>19.07075957399037</v>
+        <v>3.098998430773434</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>9.852636922090724</v>
+        <v>1.601053499839743</v>
       </c>
       <c r="D11" t="n">
-        <v>15.15547935641495</v>
+        <v>2.46276539541743</v>
       </c>
       <c r="E11" t="n">
-        <v>19.06362136088575</v>
+        <v>3.097838471143935</v>
       </c>
       <c r="F11" t="n">
-        <v>19.07075957399037</v>
+        <v>3.098998430773434</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>6.995279728571044</v>
+        <v>1.136732955892795</v>
       </c>
       <c r="D12" t="n">
-        <v>7.067016995318488</v>
+        <v>1.148390261739254</v>
       </c>
       <c r="E12" t="n">
-        <v>19.06362136088575</v>
+        <v>3.097838471143935</v>
       </c>
       <c r="F12" t="n">
-        <v>19.07075957399037</v>
+        <v>3.098998430773434</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>16.36686126884321</v>
+        <v>2.659614956187021</v>
       </c>
       <c r="D13" t="n">
-        <v>15.82936487258972</v>
+        <v>2.572271791795829</v>
       </c>
       <c r="E13" t="n">
-        <v>19.06362136088575</v>
+        <v>3.097838471143935</v>
       </c>
       <c r="F13" t="n">
-        <v>19.07075957399037</v>
+        <v>3.098998430773434</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>34.16123478476818</v>
+        <v>5.551200652524829</v>
       </c>
       <c r="D14" t="n">
-        <v>40.2927043153335</v>
+        <v>6.547564451241694</v>
       </c>
       <c r="E14" t="n">
-        <v>19.06362136088575</v>
+        <v>3.097838471143935</v>
       </c>
       <c r="F14" t="n">
-        <v>19.07075957399037</v>
+        <v>3.098998430773434</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>25.3398543472757</v>
+        <v>4.117726331432301</v>
       </c>
       <c r="D15" t="n">
-        <v>24.79333746315828</v>
+        <v>4.02891733776322</v>
       </c>
       <c r="E15" t="n">
-        <v>19.06362136088575</v>
+        <v>3.097838471143935</v>
       </c>
       <c r="F15" t="n">
-        <v>19.07075957399037</v>
+        <v>3.098998430773434</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>43.96206592473108</v>
+        <v>7.143835712768801</v>
       </c>
       <c r="D16" t="n">
-        <v>29.07797327206069</v>
+        <v>4.725170656709863</v>
       </c>
       <c r="E16" t="n">
-        <v>19.06362136088575</v>
+        <v>3.097838471143935</v>
       </c>
       <c r="F16" t="n">
-        <v>19.07075957399037</v>
+        <v>3.098998430773434</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0730860525733</v>
+        <v>5.374376483543161</v>
       </c>
       <c r="D17" t="n">
-        <v>21.38004495126622</v>
+        <v>3.47425730458076</v>
       </c>
       <c r="E17" t="n">
-        <v>19.06362136088575</v>
+        <v>3.097838471143935</v>
       </c>
       <c r="F17" t="n">
-        <v>19.07075957399037</v>
+        <v>3.098998430773434</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>47.94246219039589</v>
+        <v>7.790650105939333</v>
       </c>
       <c r="D18" t="n">
-        <v>41.46959476363494</v>
+        <v>6.738809149090678</v>
       </c>
       <c r="E18" t="n">
-        <v>19.06362136088575</v>
+        <v>3.097838471143935</v>
       </c>
       <c r="F18" t="n">
-        <v>19.07075957399037</v>
+        <v>3.098998430773434</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>48.93250712594484</v>
+        <v>7.951532407966037</v>
       </c>
       <c r="D19" t="n">
-        <v>48.85654202317485</v>
+        <v>7.939188078765913</v>
       </c>
       <c r="E19" t="n">
-        <v>19.06362136088575</v>
+        <v>3.097838471143935</v>
       </c>
       <c r="F19" t="n">
-        <v>19.07075957399037</v>
+        <v>3.098998430773434</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>46.83470009861468</v>
+        <v>7.610638766024885</v>
       </c>
       <c r="D20" t="n">
-        <v>13.86820153266882</v>
+        <v>2.253582749058683</v>
       </c>
       <c r="E20" t="n">
-        <v>19.06362136088575</v>
+        <v>3.097838471143935</v>
       </c>
       <c r="F20" t="n">
-        <v>19.07075957399037</v>
+        <v>3.098998430773434</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>36.46845640911484</v>
+        <v>5.926124166481161</v>
       </c>
       <c r="D21" t="n">
-        <v>28.68270008531476</v>
+        <v>4.660938763863648</v>
       </c>
       <c r="E21" t="n">
-        <v>19.06362136088575</v>
+        <v>3.097838471143935</v>
       </c>
       <c r="F21" t="n">
-        <v>19.07075957399037</v>
+        <v>3.098998430773434</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>51.58022150438192</v>
+        <v>8.381785994462062</v>
       </c>
       <c r="D22" t="n">
-        <v>7.746652386252574</v>
+        <v>1.258831012766043</v>
       </c>
       <c r="E22" t="n">
-        <v>19.06362136088575</v>
+        <v>3.097838471143935</v>
       </c>
       <c r="F22" t="n">
-        <v>19.07075957399037</v>
+        <v>3.098998430773434</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>42.63384782072747</v>
+        <v>6.928000270868215</v>
       </c>
       <c r="D23" t="n">
-        <v>11.23136436201566</v>
+        <v>1.825096708827545</v>
       </c>
       <c r="E23" t="n">
-        <v>19.06362136088575</v>
+        <v>3.097838471143935</v>
       </c>
       <c r="F23" t="n">
-        <v>19.07075957399037</v>
+        <v>3.098998430773434</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>58.12573425710537</v>
+        <v>9.445431816779623</v>
       </c>
       <c r="D24" t="n">
-        <v>57.31643760239254</v>
+        <v>9.313921110388788</v>
       </c>
       <c r="E24" t="n">
-        <v>19.06362136088575</v>
+        <v>3.097838471143935</v>
       </c>
       <c r="F24" t="n">
-        <v>19.07075957399037</v>
+        <v>3.098998430773434</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
